--- a/imp.xlsx
+++ b/imp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B282"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.700291063024412</v>
+        <v>0.7161983965679224</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07172454628773464</v>
+        <v>0.05193765495540378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIC0</t>
+          <t>RNCG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02789654276929821</v>
+        <v>0.02892034924549157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RNCG</t>
+          <t>SIC0</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02004378952898182</v>
+        <v>0.01592603971392937</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008264702656088096</v>
+        <v>0.009520782619193899</v>
       </c>
     </row>
     <row r="7">
@@ -497,57 +497,57 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005673934288952655</v>
+        <v>0.003335807148587512</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AETA_eta</t>
+          <t>PEOE_VSA6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00457091746545187</v>
+        <v>0.003208546111557596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PEOE_VSA6</t>
+          <t>RNCS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004197839527195202</v>
+        <v>0.002827042807855269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AATS0i</t>
+          <t>AETA_eta</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003072000103185358</v>
+        <v>0.002812481106350274</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AATSC0v</t>
+          <t>JGI5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00302082038417765</v>
+        <v>0.002776479393372399</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mor31m</t>
+          <t>IC1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002990430630276251</v>
+        <v>0.002506279876316589</v>
       </c>
     </row>
     <row r="13">
@@ -557,1557 +557,1557 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002914024951562948</v>
+        <v>0.002502902328811076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RNCS</t>
+          <t>MATS1c</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002796474478676421</v>
+        <v>0.002490556515517455</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mor26v</t>
+          <t>PEOE_VSA12</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002534408113761378</v>
+        <v>0.002465766788525392</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EState_VSA4</t>
+          <t>AATS0i</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002385015866010909</v>
+        <v>0.002449934707639942</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MATS1c</t>
+          <t>Mor02m</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002381303642984886</v>
+        <v>0.002326572174083548</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AATS0se</t>
+          <t>nHRing</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002329249847739658</v>
+        <v>0.002240705812361456</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mor02m</t>
+          <t>AATS0se</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002208525036245457</v>
+        <v>0.002181134393170787</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATSC2c</t>
+          <t>AATSC0v</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.002152519548114793</v>
+        <v>0.00212358944049833</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC0</t>
+          <t>ATSC8v</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.002142437919864609</v>
+        <v>0.002096437693162183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PEOE_VSA8</t>
+          <t>ATSC4dv</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.002129277484169786</v>
+        <v>0.001928459876111539</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PEOE_VSA2</t>
+          <t>RPCS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001926327015257475</v>
+        <v>0.001828638280149354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ATSC1se</t>
+          <t>GATS1se</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0018619007269132</v>
+        <v>0.001731623204181569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JGI5</t>
+          <t>Mor14m</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001719029402769828</v>
+        <v>0.001647342251928954</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mor12m</t>
+          <t>EState_VSA4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001707635687553494</v>
+        <v>0.001627090123925199</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FPSA3</t>
+          <t>ATSC8se</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001583732354537448</v>
+        <v>0.001612001481556944</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mor22m</t>
+          <t>ATSC8d</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001574901334001771</v>
+        <v>0.001578913663268103</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mor04</t>
+          <t>ATSC6dv</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001488465673748792</v>
+        <v>0.001554453153011997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETA_shape_y</t>
+          <t>FPSA3</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001470158402735674</v>
+        <v>0.001545927966762183</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mor32m</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001434035666560311</v>
+        <v>0.00152150688689968</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mor32</t>
+          <t>ATSC1se</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001396721631788734</v>
+        <v>0.001504273388637972</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VR1_A</t>
+          <t>Mor12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001373722296222654</v>
+        <v>0.001493428445725314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ATSC4dv</t>
+          <t>PEOE_VSA2</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001335831448100009</v>
+        <v>0.001426230672552436</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AATS0dv</t>
+          <t>ATSC3i</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001286283372812604</v>
+        <v>0.001405700085731122</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RPCS</t>
+          <t>ATSC7c</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001274809618066349</v>
+        <v>0.001402437125731392</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mor09</t>
+          <t>ATSC6d</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.001250980072600822</v>
+        <v>0.001384613844314902</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IC1</t>
+          <t>PEOE_VSA8</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001193837081722794</v>
+        <v>0.001352099898152377</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GATS2se</t>
+          <t>Mor21m</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.001149831419307357</v>
+        <v>0.001337711055953858</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GATS1se</t>
+          <t>Mor04m</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.001129844206529017</v>
+        <v>0.001309382941017371</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EState_VSA8</t>
+          <t>ATSC2c</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.001098051032172144</v>
+        <v>0.001291878447967589</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mor20m</t>
+          <t>AATSC2Z</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.001083835994224979</v>
+        <v>0.001272575448856296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCUTZ-1l</t>
+          <t>VR1_A</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.001068284053461543</v>
+        <v>0.001232254518879518</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mor29</t>
+          <t>Mor26m</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0010670145882111</v>
+        <v>0.001209376323612355</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BalabanJ</t>
+          <t>GATS2se</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.001064166790970126</v>
+        <v>0.001206042336047793</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ATSC2Z</t>
+          <t>ATSC7dv</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.001056137359261277</v>
+        <v>0.001189377751042615</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mor04m</t>
+          <t>Mor13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001056017740157199</v>
+        <v>0.001183302876197457</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMID_O</t>
+          <t>Mor32m</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.001051411180518613</v>
+        <v>0.001181285078452377</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mor26m</t>
+          <t>Mor22m</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.001043144138773687</v>
+        <v>0.001159936740876684</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ATSC3i</t>
+          <t>Mor17m</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.001040604511519362</v>
+        <v>0.001124776972289232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NaaN</t>
+          <t>Mor11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.001036082349025275</v>
+        <v>0.001112498420339352</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mor21m</t>
+          <t>nHetero</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.001017343896421396</v>
+        <v>0.001104085063097341</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mor09m</t>
+          <t>AATSC0i</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.001014293457133791</v>
+        <v>0.001099273554390121</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GATS1Z</t>
+          <t>Mor06m</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.00101119451730352</v>
+        <v>0.001097639994167595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mor18m</t>
+          <t>Mor04v</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.001008403404959462</v>
+        <v>0.001096138917690849</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mor14m</t>
+          <t>Mor19m</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.001005210550747879</v>
+        <v>0.001085361836988653</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PEOE_VSA7</t>
+          <t>BCUTd-1l</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0009843124697232375</v>
+        <v>0.001076984293903976</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mor06m</t>
+          <t>GeomShapeIndex</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0009720515708953438</v>
+        <v>0.001047948354096088</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JGI7</t>
+          <t>ATSC4se</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0009207666153952025</v>
+        <v>0.001038172509514111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mor19m</t>
+          <t>Mor31m</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0009077424427608296</v>
+        <v>0.001026806905558922</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>nHetero</t>
+          <t>Mor11v</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0008972484373200744</v>
+        <v>0.001024481467136829</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mor30</t>
+          <t>ETA_shape_y</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0008851733338983123</v>
+        <v>0.001023467556020178</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ATSC6d</t>
+          <t>AATS0dv</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0008843165197858281</v>
+        <v>0.001021829951002046</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mor10</t>
+          <t>PEOE_VSA7</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0008699530469187066</v>
+        <v>0.001006580017643169</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ATSC1i</t>
+          <t>ETA_dBeta</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0008664686666810157</v>
+        <v>0.001005603955059744</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ATSC4se</t>
+          <t>MATS1Z</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.00086167828473063</v>
+        <v>0.001005491514892508</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ATSC6dv</t>
+          <t>Mor29</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.000860217306844904</v>
+        <v>0.0009676950923330894</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mor13</t>
+          <t>Mor26v</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0008531833345483175</v>
+        <v>0.0009650142337108153</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ATSC8dv</t>
+          <t>SaasC</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0008387966509842484</v>
+        <v>0.0009583016700344141</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AATSC0i</t>
+          <t>EState_VSA5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0008171664708924085</v>
+        <v>0.0009551520388419681</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mor28v</t>
+          <t>ATSC6Z</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0008123111202908207</v>
+        <v>0.0009449360073936577</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mor16</t>
+          <t>BCUTc-1l</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0008094163910529152</v>
+        <v>0.0009444239238370518</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mor11m</t>
+          <t>Mor20m</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0008072264478129406</v>
+        <v>0.0009419025567180026</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ATSC3d</t>
+          <t>Mor30m</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.00080127024330395</v>
+        <v>0.0009407831096241843</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ATSC4Z</t>
+          <t>MATS2Z</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0007891224418337505</v>
+        <v>0.0009362173953270495</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EState_VSA7</t>
+          <t>ATSC4c</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0007791423413310603</v>
+        <v>0.0009277745049720579</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MATS2Z</t>
+          <t>Mor32</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0007695946994828382</v>
+        <v>0.0009191889459023375</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mor24v</t>
+          <t>Mor10</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0007664752144752022</v>
+        <v>0.0009082274729489166</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mor12</t>
+          <t>Mor28</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0007580725780217321</v>
+        <v>0.0009026556920492949</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mor28m</t>
+          <t>EState_VSA8</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0007574966402774364</v>
+        <v>0.0008931073646629846</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mor24</t>
+          <t>ATSC1p</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0007500876832952428</v>
+        <v>0.0008898719059481138</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCUTd-1l</t>
+          <t>Mor13m</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0007430763626417616</v>
+        <v>0.0008685773147997508</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ATSC7dv</t>
+          <t>AMID_O</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0007421514847864525</v>
+        <v>0.0008655199011279711</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mor13m</t>
+          <t>IC0</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0007414763956071311</v>
+        <v>0.0008603390162123163</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ATSC2dv</t>
+          <t>ATSC8c</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0007372395313165974</v>
+        <v>0.0008588402076496496</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mor17m</t>
+          <t>ATSC4Z</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0007367218510585022</v>
+        <v>0.0008542699601046822</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GATS2c</t>
+          <t>SdssC</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0007279256805775275</v>
+        <v>0.0008425908963334989</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ATSC1p</t>
+          <t>ATSC7d</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0007222797661369189</v>
+        <v>0.0008349535120781437</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ATSC6Z</t>
+          <t>Mor27m</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0007175003057639473</v>
+        <v>0.0008232349559490861</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PEOE_VSA9</t>
+          <t>Mor26</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0006965756661067818</v>
+        <v>0.0008226806274795898</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mor23m</t>
+          <t>Mor30</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0006952004351698986</v>
+        <v>0.0008096119729920534</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mor29m</t>
+          <t>JGI3</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0006912489262287325</v>
+        <v>0.0008061038806653317</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Mor09</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0006902738222683647</v>
+        <v>0.0008017070545625572</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GeomShapeIndex</t>
+          <t>PBF</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0006885605094893135</v>
+        <v>0.0007907026181940142</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mor16m</t>
+          <t>GATS2i</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.0006863227531994917</v>
+        <v>0.00079049463928953</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ATSC5d</t>
+          <t>ATSC5c</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0006839038710961716</v>
+        <v>0.0007832343701200697</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SpMAD_A</t>
+          <t>Mor23m</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0006822568718049405</v>
+        <v>0.0007776834052096936</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ETA_dBeta</t>
+          <t>ATSC5Z</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0006779084586270768</v>
+        <v>0.0007636515017902448</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ATSC3dv</t>
+          <t>Mor10v</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0006775310735782105</v>
+        <v>0.0007587513831601469</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ATSC5dv</t>
+          <t>BCUTZ-1l</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.000674788015864625</v>
+        <v>0.0007536693425437208</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ATSC8d</t>
+          <t>BalabanJ</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0006696737899452125</v>
+        <v>0.0007499137805502787</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ATSC5se</t>
+          <t>ATSC3d</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0006657066202313377</v>
+        <v>0.0007361268969096625</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mor08</t>
+          <t>ATSC8dv</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0006617574288794456</v>
+        <v>0.0007292535914876483</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mor04v</t>
+          <t>Mor24m</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0006558188535081874</v>
+        <v>0.000728763932969447</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SaasC</t>
+          <t>Mor16</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0006459677278525047</v>
+        <v>0.0007247173892219823</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ATSC5i</t>
+          <t>Mor24</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0006423019328425928</v>
+        <v>0.0007241039122977702</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mor24m</t>
+          <t>Mor12m</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0006418067402766353</v>
+        <v>0.0007235439201022815</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mor15</t>
+          <t>GATS2c</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0006322779843705394</v>
+        <v>0.000712252677805304</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ATSC4v</t>
+          <t>ATSC5se</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0006280678506735888</v>
+        <v>0.0006907145146432675</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GATS2v</t>
+          <t>Mor15m</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0006160642044787473</v>
+        <v>0.0006825496160229245</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mor26</t>
+          <t>ATSC1i</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0006140758066909162</v>
+        <v>0.0006808538220129878</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mor10v</t>
+          <t>PEOE_VSA9</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0006136990776947219</v>
+        <v>0.0006788827809743718</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ATSC6se</t>
+          <t>ATSC8Z</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0006133606482954226</v>
+        <v>0.0006778104671699691</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Mor30m</t>
+          <t>ATSC3se</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0006119872344824819</v>
+        <v>0.0006727204364823576</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mor10m</t>
+          <t>ATSC2Z</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0006111515046427707</v>
+        <v>0.0006634443683231139</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ATSC3Z</t>
+          <t>Mor28v</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0006110980582992199</v>
+        <v>0.0006576163831143888</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCUTc-1l</t>
+          <t>Mor11m</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0006109084209605012</v>
+        <v>0.0006570090738837763</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ATSC6c</t>
+          <t>NaaN</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0006055609784038549</v>
+        <v>0.0006483793807185024</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Mor22</t>
+          <t>ATSC7se</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0006041773082037336</v>
+        <v>0.0006476336300622021</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GATS2i</t>
+          <t>Mor27</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0005997078341310127</v>
+        <v>0.00064046115460303</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ATSC7se</t>
+          <t>ATSC6se</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0005832737357074273</v>
+        <v>0.0006217699955357114</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ATSC8se</t>
+          <t>SlogP_VSA3</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0005816830042523752</v>
+        <v>0.0006120911649466499</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mor28</t>
+          <t>ATSC5dv</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0005809405472227752</v>
+        <v>0.0006103848306112045</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SIC1</t>
+          <t>Mor16m</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.000579809212793961</v>
+        <v>0.0006058731900315317</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JGI8</t>
+          <t>ATSC4v</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0005726043301855591</v>
+        <v>0.0006031889365994187</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PEOE_VSA12</t>
+          <t>SpMAD_A</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0005710024114983074</v>
+        <v>0.0005967373847022799</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JGI4</t>
+          <t>ATSC7Z</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0005641264878627044</v>
+        <v>0.000595995691947775</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>nHRing</t>
+          <t>GATS1Z</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0005599180895089161</v>
+        <v>0.0005958720030102082</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ATSC4c</t>
+          <t>ATSC3Z</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0005598818429631124</v>
+        <v>0.0005924092883512001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ATSC8v</t>
+          <t>Mor29m</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.000557293489549874</v>
+        <v>0.0005880735214949473</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ATSC1Z</t>
+          <t>ATSC2d</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0005496847094501728</v>
+        <v>0.0005850305835941067</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ATSC5v</t>
+          <t>Mor10m</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0005295811402977534</v>
+        <v>0.0005761896147247984</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ATSC3v</t>
+          <t>ATSC2v</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0005292042192298919</v>
+        <v>0.0005716222841420673</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ATSC6i</t>
+          <t>ATSC5d</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.0005253961299782281</v>
+        <v>0.0005686879724449497</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PEOE_VSA10</t>
+          <t>Mor25m</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0005235071197798804</v>
+        <v>0.0005641589731165002</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EState_VSA2</t>
+          <t>SIC1</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0005209702169014554</v>
+        <v>0.0005616881861880252</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ATSC1v</t>
+          <t>GATS2Z</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.0005182387823551056</v>
+        <v>0.000561117816538301</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EState_VSA5</t>
+          <t>Mor18</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0005144802870443487</v>
+        <v>0.0005566021264205853</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mor27</t>
+          <t>EState_VSA3</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.0005105897684818525</v>
+        <v>0.0005543095795657479</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ATSC3se</t>
+          <t>Mor15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.0005031700462095969</v>
+        <v>0.0005494439617844759</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Mor11v</t>
+          <t>ATSC7i</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0004988985365511803</v>
+        <v>0.0005368670952821302</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Mor11</t>
+          <t>VSA_EState5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0004924547310878788</v>
+        <v>0.0005359159315438772</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mor27m</t>
+          <t>EState_VSA7</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0004913349133042981</v>
+        <v>0.0005314517554799286</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ATSC5c</t>
+          <t>Mor18m</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.0004882032630749477</v>
+        <v>0.000528091979043592</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VSA_EState4</t>
+          <t>Mor09m</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0004816888236110605</v>
+        <v>0.0005264246837312517</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ATSC4d</t>
+          <t>AATSC1d</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.000470792754007281</v>
+        <v>0.0005161333257769702</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VSA_EState5</t>
+          <t>ATSC3v</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0004704243653589429</v>
+        <v>0.0005104783664841404</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ATSC2d</t>
+          <t>ATSC3dv</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0004667792727850808</v>
+        <v>0.0005034004859806822</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ATSC8Z</t>
+          <t>ATSC6i</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0004667688225985236</v>
+        <v>0.0005014103807855441</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ATSC7c</t>
+          <t>SlogP_VSA4</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.0004560829538333883</v>
+        <v>0.0004998584873935165</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PBF</t>
+          <t>Mor24v</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0004508034679596881</v>
+        <v>0.0004964128493934678</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ATSC8c</t>
+          <t>ATSC5i</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0004437440210808698</v>
+        <v>0.0004868704843334161</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ATSC7i</t>
+          <t>Mor08</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0004379692210643965</v>
+        <v>0.0004866721673474161</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCUTdv-1l</t>
+          <t>ATSC4d</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0004362358743809356</v>
+        <v>0.0004838740526257996</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ATSC2i</t>
+          <t>Mor06</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0004345374641245743</v>
+        <v>0.0004828034261564471</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Mor15m</t>
+          <t>ATSC5v</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.0004337889809541791</v>
+        <v>0.0004615062896337799</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AATS0Z</t>
+          <t>BCUTd-1h</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0004308245343780444</v>
+        <v>0.0004533313427302933</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AATSC1d</t>
+          <t>BCUTdv-1l</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0004123373052179779</v>
+        <v>0.0004529196294920538</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mor06</t>
+          <t>GATS2v</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0004094419983507263</v>
+        <v>0.0004507611766451422</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MATS1Z</t>
+          <t>EState_VSA2</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.0004068576373982996</v>
+        <v>0.0004496385591276352</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ATSC1dv</t>
+          <t>ATSC6v</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.0004032485457107113</v>
+        <v>0.0004457201348280892</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>JGI2</t>
+          <t>ATSC8i</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.0004027156058700864</v>
+        <v>0.000444064887407964</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JGI9</t>
+          <t>JGI2</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0003989340903740243</v>
+        <v>0.0004431496624862394</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ATSC7Z</t>
+          <t>Mor04</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0003933882333257068</v>
+        <v>0.0004423848293182013</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ATSC2v</t>
+          <t>JGI4</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.0003899839229017403</v>
+        <v>0.0004377033498135131</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AETA_eta_RL</t>
+          <t>Mor22</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.0003820671493159096</v>
+        <v>0.0004309767664283248</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GATS2Z</t>
+          <t>Mor28m</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.0003767922482400077</v>
+        <v>0.0004275150322440972</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ATSC7d</t>
+          <t>VSA_EState1</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0003709293914046137</v>
+        <v>0.0004185530241062437</v>
       </c>
     </row>
     <row r="169">
@@ -2117,457 +2117,457 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.0003663921633707933</v>
+        <v>0.0004151466514398756</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AATSC2Z</t>
+          <t>ATSC6c</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0003649165868694711</v>
+        <v>0.0004124314214893211</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BCUTd-1h</t>
+          <t>JGI1</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.0003540676297322917</v>
+        <v>0.0003994957785174376</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JGI3</t>
+          <t>nS</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0003535420534672292</v>
+        <v>0.0003976489349727739</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JGI6</t>
+          <t>JGI10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.0003467033246373179</v>
+        <v>0.000397644688920444</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C1SP2</t>
+          <t>ATSC1Z</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.0003303778648139639</v>
+        <v>0.0003970076799204025</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ATSC5Z</t>
+          <t>nRot</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.0003263085721561579</v>
+        <v>0.0003932498196776664</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EState_VSA3</t>
+          <t>JGI6</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0003218917891599521</v>
+        <v>0.0003887344801592921</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NaasC</t>
+          <t>ATSC2dv</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0003150130870946287</v>
+        <v>0.0003885342437972496</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SMR_VSA6</t>
+          <t>ATSC2i</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.0003144553278984672</v>
+        <v>0.0003799581738848388</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SdssC</t>
+          <t>ATSC1v</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.0002990350870605186</v>
+        <v>0.0003754840438541627</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ETA_beta_ns_d</t>
+          <t>GhoseFilter</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.000286839700855886</v>
+        <v>0.0003680325747419268</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ATSC6v</t>
+          <t>ATSC1dv</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.0002860357413149839</v>
+        <v>0.0003506801683097912</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SlogP_VSA3</t>
+          <t>AETA_eta_RL</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.0002796432677190876</v>
+        <v>0.0003456116790010406</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>JGI1</t>
+          <t>VSA_EState4</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.0002782032029825541</v>
+        <v>0.0003365180932059764</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ATSC8i</t>
+          <t>JGI8</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0002358602019408311</v>
+        <v>0.0003060549430827697</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>VSA_EState9</t>
+          <t>SlogP_VSA10</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0002302363075042763</v>
+        <v>0.0003024103399697671</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SlogP_VSA1</t>
+          <t>C1SP2</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.0002291968174385723</v>
+        <v>0.000280796140683086</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>nRot</t>
+          <t>SlogP_VSA1</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.0002281840117881223</v>
+        <v>0.0002668978022801282</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>n10FHRing</t>
+          <t>AATS0Z</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.0002274246667971326</v>
+        <v>0.0002541676057100416</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>VSA_EState1</t>
+          <t>NaasC</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.0002264791055269127</v>
+        <v>0.0002315878829410822</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PEOE_VSA5</t>
+          <t>JGI7</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.0002259228979400342</v>
+        <v>0.000229218891913289</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C2SP3</t>
+          <t>PEOE_VSA10</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.0002165187007202633</v>
+        <v>0.0002205966749803808</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EState_VSA6</t>
+          <t>nN</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.0002097736298501562</v>
+        <v>0.0002071301636161499</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>nAromAtom</t>
+          <t>C1SP3</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.0002078694632589859</v>
+        <v>0.0002025653719854349</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SsssCH</t>
+          <t>EState_VSA6</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.000203798118005488</v>
+        <v>0.000201684546506143</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SlogP_VSA10</t>
+          <t>n10FHRing</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0001905257989281512</v>
+        <v>0.0001981102285371866</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>NdsCH</t>
+          <t>JGI9</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.0001852358531602433</v>
+        <v>0.0001936942832337281</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C1SP3</t>
+          <t>PEOE_VSA11</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.0001799211930986502</v>
+        <v>0.0001916391919019317</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nFaHRing</t>
+          <t>SsssCH</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0001759376331588077</v>
+        <v>0.0001879259487191776</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FCSP3</t>
+          <t>NaasN</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0001719927267238164</v>
+        <v>0.0001825993459890283</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GhoseFilter</t>
+          <t>C2SP3</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.000164815893550058</v>
+        <v>0.0001728927276994249</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>NssNH</t>
+          <t>ETA_beta_ns_d</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.0001609686327984223</v>
+        <v>0.0001606284459061021</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SMR_VSA9</t>
+          <t>FCSP3</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.0001570210939960663</v>
+        <v>0.0001572181708530253</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Xc-4dv</t>
+          <t>NssNH</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.0001440091302748593</v>
+        <v>0.0001572107572862548</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NsssCH</t>
+          <t>nFHRing</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.0001302741415491159</v>
+        <v>0.0001512487785098273</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SlogP_VSA7</t>
+          <t>Xc-4d</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.0001301658708659924</v>
+        <v>0.0001499437075563997</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PEOE_VSA11</t>
+          <t>NssS</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.0001301055657704512</v>
+        <v>0.00013802757340478</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>JGI10</t>
+          <t>n5Ring</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.0001254721677866584</v>
+        <v>0.0001316408118867662</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SlogP_VSA4</t>
+          <t>PEOE_VSA3</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.0001170828090472556</v>
+        <v>0.0001305841576262732</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>nN</t>
+          <t>SMR_VSA6</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.0001082409521131225</v>
+        <v>0.0001225934313000122</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PEOE_VSA4</t>
+          <t>nFRing</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.0001075904782783189</v>
+        <v>0.0001207859457357173</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PEOE_VSA3</t>
+          <t>nAromAtom</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.0001034789926240274</v>
+        <v>0.0001053648646655636</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NsCH3</t>
+          <t>nO</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>9.36734235525142e-05</v>
+        <v>0.0001037022658468435</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>nFHRing</t>
+          <t>SMR_VSA9</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>9.343090551143197e-05</v>
+        <v>9.434393442922134e-05</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>NssO</t>
+          <t>Xc-4dv</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>9.216699471688134e-05</v>
+        <v>9.430533804049388e-05</v>
       </c>
     </row>
     <row r="215">
@@ -2577,27 +2577,27 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>9.099350662876478e-05</v>
+        <v>9.391727194395687e-05</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>nHBDon</t>
+          <t>PEOE_VSA13</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>8.681330637971921e-05</v>
+        <v>8.850294880409318e-05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>nFARing</t>
+          <t>nAHRing</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>8.607673499716496e-05</v>
+        <v>8.271998323806023e-05</v>
       </c>
     </row>
     <row r="218">
@@ -2607,217 +2607,217 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>8.59392307929412e-05</v>
+        <v>6.775319834741427e-05</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>nP</t>
+          <t>VSA_EState9</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>8.038880366560937e-05</v>
+        <v>6.338066281550583e-05</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>nBondsD</t>
+          <t>NsOH</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>7.276249608266805e-05</v>
+        <v>6.284914255423481e-05</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>nFRing</t>
+          <t>nFAHRing</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7.14743837691181e-05</v>
+        <v>5.99586037769308e-05</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C3SP2</t>
+          <t>n6AHRing</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>6.835616691971158e-05</v>
+        <v>5.623605240678376e-05</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>nO</t>
+          <t>SlogP_VSA7</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>6.178015090315372e-05</v>
+        <v>5.036494448971363e-05</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Xc-4d</t>
+          <t>nBondsD</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>5.857424672735746e-05</v>
+        <v>4.892881196096795e-05</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C3SP3</t>
+          <t>NdsCH</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>5.455279212583343e-05</v>
+        <v>4.618760972902601e-05</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SlogP_VSA11</t>
+          <t>NsssCH</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>5.169136895580031e-05</v>
+        <v>4.161078102027078e-05</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>NaasN</t>
+          <t>NddsN</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>4.830316378590839e-05</v>
+        <v>3.800316542378009e-05</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>n5Ring</t>
+          <t>C4SP3</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>3.677704538692203e-05</v>
+        <v>3.669189866286738e-05</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NsOH</t>
+          <t>SlogP_VSA11</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>3.6533016606844e-05</v>
+        <v>3.524097733031543e-05</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NsssN</t>
+          <t>NsCH3</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3.612552748097609e-05</v>
+        <v>3.396790708495359e-05</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>nAHRing</t>
+          <t>C3SP2</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2.893399223515644e-05</v>
+        <v>3.106357713062097e-05</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PEOE_VSA13</t>
+          <t>PEOE_VSA5</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.891385474225817e-05</v>
+        <v>3.037581518601121e-05</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NdsN</t>
+          <t>nP</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.873452345784693e-05</v>
+        <v>2.769264390625356e-05</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NaaNH</t>
+          <t>nCl</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.690286092305903e-05</v>
+        <v>2.513638931939241e-05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>nF</t>
+          <t>nHBDon</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.425488509844535e-05</v>
+        <v>2.481265720570904e-05</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>n6AHRing</t>
+          <t>nF</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.416697662913966e-05</v>
+        <v>2.391919162381689e-05</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>nFAHRing</t>
+          <t>n5AHRing</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.307402355320233e-05</v>
+        <v>2.334358674422491e-05</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C4SP3</t>
+          <t>nFaHRing</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1.138244833974489e-05</v>
+        <v>2.31406525403019e-05</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>NaaaC</t>
+          <t>C3SP3</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.014308748711945e-05</v>
+        <v>2.243166808613954e-05</v>
       </c>
     </row>
     <row r="240">
@@ -2827,257 +2827,257 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>9.487252036838114e-06</v>
+        <v>2.029530036309131e-05</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>nCl</t>
+          <t>NsssN</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7.299566960933076e-06</v>
+        <v>1.608567885895374e-05</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NssS</t>
+          <t>NssO</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>7.13986270985534e-06</v>
+        <v>1.543149274207351e-05</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>nS</t>
+          <t>NaaaC</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>6.995481283398084e-06</v>
+        <v>1.330169188948977e-05</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>n9FRing</t>
+          <t>nSpiro</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>5.597684028758769e-06</v>
+        <v>1.151098044449884e-05</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>nG12FRing</t>
+          <t>n5aRing</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>5.399941126811431e-06</v>
+        <v>1.143290808894677e-05</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>NaaO</t>
+          <t>PEOE_VSA4</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>4.559868540083068e-06</v>
+        <v>1.074471789441285e-05</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>nBondsT</t>
+          <t>n10FARing</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>4.281597918332376e-06</v>
+        <v>8.105118406881577e-06</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>nBr</t>
+          <t>Xch-3d</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>3.554101463380191e-06</v>
+        <v>5.438680578882899e-06</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>n5AHRing</t>
+          <t>n9FARing</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>3.462130678641358e-06</v>
+        <v>4.633555960654199e-06</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>n9FaRing</t>
+          <t>Xch-4d</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>2.839374422601402e-06</v>
+        <v>4.368742052093199e-06</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>n10FARing</t>
+          <t>NaaNH</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>2.745132723132432e-06</v>
+        <v>4.166215378859287e-06</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C2SP1</t>
+          <t>nG12FHRing</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2.686057287279103e-06</v>
+        <v>3.602878713387149e-06</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>NsNH2</t>
+          <t>NdsN</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2.122460182397528e-06</v>
+        <v>3.345803172577636e-06</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Xch-3d</t>
+          <t>nG12FRing</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>2.039794526303321e-06</v>
+        <v>3.312024467483284e-06</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>n9FARing</t>
+          <t>NdCH2</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>1.306066727685479e-06</v>
+        <v>3.280076192293317e-06</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>NdCH2</t>
+          <t>nBondsT</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1.129788205951014e-06</v>
+        <v>2.883461027205756e-06</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>NtN</t>
+          <t>nFARing</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1.022303387795022e-06</v>
+        <v>2.776222910437036e-06</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>NaaS</t>
+          <t>NsNH2</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1.014078240516593e-06</v>
+        <v>2.772773890665994e-06</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>NtCH</t>
+          <t>NaaO</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>7.561173793186066e-07</v>
+        <v>2.662630326737586e-06</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>NddssS</t>
+          <t>NtN</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>5.690139964240083e-07</v>
+        <v>2.372705723703139e-06</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>n5aRing</t>
+          <t>C2SP1</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>4.966906969032737e-07</v>
+        <v>2.081746723844519e-06</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>n10FAHRing</t>
+          <t>NtCH</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>4.411109701205242e-07</v>
+        <v>1.785012662362539e-06</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>nG12FHRing</t>
+          <t>nBr</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>4.281133964825471e-07</v>
+        <v>1.451469246634855e-06</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>n8FRing</t>
+          <t>n9FRing</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2.982362686096645e-07</v>
+        <v>9.311810077145369e-07</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>nBridgehead</t>
+          <t>n11FRing</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>2.909832154042228e-07</v>
+        <v>8.122619228317521e-07</v>
       </c>
     </row>
     <row r="266">
@@ -3087,47 +3087,47 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>2.731055483135299e-07</v>
+        <v>5.257759014967981e-07</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>NddsN</t>
+          <t>n7Ring</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2.59007351367807e-07</v>
+        <v>4.819466010962238e-07</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>n12FHRing</t>
+          <t>n9FaRing</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>2.263716517671221e-07</v>
+        <v>6.346213282381802e-08</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NsSH</t>
+          <t>nBridgehead</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>2.003916873131407e-07</v>
+        <v>5.908213295067846e-08</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Xch-4d</t>
+          <t>nBase</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1.633201140340218e-07</v>
+        <v>4.198952049675499e-08</v>
       </c>
     </row>
     <row r="271">
@@ -3137,93 +3137,93 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1.509209656266737e-07</v>
+        <v>1.847262295193868e-08</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>nG12FaHRing</t>
+          <t>n8FRing</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1.505875476121656e-07</v>
+        <v>1.522599155070745e-08</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>n7Ring</t>
+          <t>NddssS</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>1.44225112851441e-07</v>
+        <v>5.67662063574839e-09</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>nSpiro</t>
+          <t>nG12FaHRing</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>5.602564501805761e-08</v>
+        <v>2.013354254599248e-09</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>n3HRing</t>
+          <t>n10FAHRing</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>4.446188073986005e-08</v>
+        <v>1.620775078068902e-10</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>n12FRing</t>
+          <t>n12FHRing</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3.877107730568257e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>n7FRing</t>
+          <t>NaaS</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1.557944816950631e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>nBase</t>
+          <t>NsSH</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>7.516333931946661e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>NdssS</t>
+          <t>NdNH</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>5.766923180208341e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>NdNH</t>
+          <t>NdssS</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3243,10 +3243,30 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>n11FRing</t>
+          <t>n3HRing</t>
         </is>
       </c>
       <c r="B282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>n12FRing</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>n7FRing</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
         <v>0</v>
       </c>
     </row>

--- a/imp.xlsx
+++ b/imp.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7161983965679224</v>
+        <v>0.7198314864812727</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05193765495540378</v>
+        <v>0.04926555841978541</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02892034924549157</v>
+        <v>0.02738199076512673</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01592603971392937</v>
+        <v>0.01678279661849459</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009520782619193899</v>
+        <v>0.01015521877504702</v>
       </c>
     </row>
     <row r="7">
@@ -497,57 +497,57 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003335807148587512</v>
+        <v>0.003527252964672561</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PEOE_VSA6</t>
+          <t>JGI5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003208546111557596</v>
+        <v>0.003427386685605978</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RNCS</t>
+          <t>AETA_eta</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002827042807855269</v>
+        <v>0.003100126482830602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AETA_eta</t>
+          <t>Mor02m</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002812481106350274</v>
+        <v>0.003071434040517759</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JGI5</t>
+          <t>RNCS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002776479393372399</v>
+        <v>0.00272196428518121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC1</t>
+          <t>PEOE_VSA6</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002506279876316589</v>
+        <v>0.002430164482882451</v>
       </c>
     </row>
     <row r="13">
@@ -557,227 +557,227 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002502902328811076</v>
+        <v>0.002334851112888123</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MATS1c</t>
+          <t>FPSA3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002490556515517455</v>
+        <v>0.002277061151548345</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PEOE_VSA12</t>
+          <t>AATS0i</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002465766788525392</v>
+        <v>0.002265334089025447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AATS0i</t>
+          <t>AATS0se</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002449934707639942</v>
+        <v>0.002181598516803452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mor02m</t>
+          <t>MATS1c</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002326572174083548</v>
+        <v>0.002071132448100907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nHRing</t>
+          <t>Mor22m</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002240705812361456</v>
+        <v>0.002044934513369181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AATS0se</t>
+          <t>IC1</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002181134393170787</v>
+        <v>0.001991386153980218</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AATSC0v</t>
+          <t>ATSC8v</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.00212358944049833</v>
+        <v>0.001984453170248523</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ATSC8v</t>
+          <t>AATSC0v</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.002096437693162183</v>
+        <v>0.001961026246939188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ATSC4dv</t>
+          <t>PEOE_VSA12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001928459876111539</v>
+        <v>0.001915528251448839</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RPCS</t>
+          <t>IC0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001828638280149354</v>
+        <v>0.001842464034987681</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GATS1se</t>
+          <t>nHRing</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001731623204181569</v>
+        <v>0.001775022577756296</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mor14m</t>
+          <t>ATSC7dv</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.001647342251928954</v>
+        <v>0.00177083892603931</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EState_VSA4</t>
+          <t>ATSC6dv</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001627090123925199</v>
+        <v>0.001770216477181981</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ATSC8se</t>
+          <t>SaasC</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001612001481556944</v>
+        <v>0.001750610197467569</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ATSC8d</t>
+          <t>GATS1se</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001578913663268103</v>
+        <v>0.001703977456023297</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ATSC6dv</t>
+          <t>ATSC1se</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001554453153011997</v>
+        <v>0.001583554948246597</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FPSA3</t>
+          <t>GATS2se</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001545927966762183</v>
+        <v>0.001571924688314876</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>ATSC3i</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.00152150688689968</v>
+        <v>0.001560790903433062</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ATSC1se</t>
+          <t>ATSC4dv</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001504273388637972</v>
+        <v>0.001522844416422335</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mor12</t>
+          <t>PEOE_VSA7</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001493428445725314</v>
+        <v>0.001477540542666759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PEOE_VSA2</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001426230672552436</v>
+        <v>0.001450057860045733</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ATSC3i</t>
+          <t>Mor14m</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001405700085731122</v>
+        <v>0.001418156579363753</v>
       </c>
     </row>
     <row r="36">
@@ -787,877 +787,877 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001402437125731392</v>
+        <v>0.001402673155561526</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ATSC6d</t>
+          <t>ATSC6Z</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.001384613844314902</v>
+        <v>0.001318673889878545</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PEOE_VSA8</t>
+          <t>AATS0dv</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001352099898152377</v>
+        <v>0.001300293708984733</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mor21m</t>
+          <t>AATSC2Z</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.001337711055953858</v>
+        <v>0.00129503408943568</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mor04m</t>
+          <t>Mor32</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.001309382941017371</v>
+        <v>0.00129448211301305</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ATSC2c</t>
+          <t>MATS2Z</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.001291878447967589</v>
+        <v>0.001232134087847298</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AATSC2Z</t>
+          <t>Mor17m</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.001272575448856296</v>
+        <v>0.001211084211327553</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VR1_A</t>
+          <t>ATSC6d</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.001232254518879518</v>
+        <v>0.00120482942898372</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mor26m</t>
+          <t>Mor32m</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.001209376323612355</v>
+        <v>0.001199746381469413</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GATS2se</t>
+          <t>Mor21m</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.001206042336047793</v>
+        <v>0.001198505835932385</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ATSC7dv</t>
+          <t>Mor30m</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.001189377751042615</v>
+        <v>0.001169280800721781</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mor13</t>
+          <t>RPCS</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001183302876197457</v>
+        <v>0.001161588014855488</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mor32m</t>
+          <t>nHetero</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.001181285078452377</v>
+        <v>0.001148710846320247</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mor22m</t>
+          <t>Mor29</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.001159936740876684</v>
+        <v>0.001142579539377084</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mor17m</t>
+          <t>Mor26v</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.001124776972289232</v>
+        <v>0.00114133536179568</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mor11</t>
+          <t>EState_VSA4</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.001112498420339352</v>
+        <v>0.001141181832125424</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nHetero</t>
+          <t>Mor27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.001104085063097341</v>
+        <v>0.00114081585881781</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AATSC0i</t>
+          <t>Mor04v</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.001099273554390121</v>
+        <v>0.001125046026919892</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mor06m</t>
+          <t>AATSC0i</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.001097639994167595</v>
+        <v>0.001121387981094643</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mor04v</t>
+          <t>BCUTc-1l</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.001096138917690849</v>
+        <v>0.001117316113650834</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mor19m</t>
+          <t>Mor06m</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.001085361836988653</v>
+        <v>0.001107090818040895</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCUTd-1l</t>
+          <t>GeomShapeIndex</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.001076984293903976</v>
+        <v>0.001089582234277316</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GeomShapeIndex</t>
+          <t>EState_VSA8</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.001047948354096088</v>
+        <v>0.00105963805637794</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ATSC4se</t>
+          <t>ATSC2c</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.001038172509514111</v>
+        <v>0.001056216187527707</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mor31m</t>
+          <t>VR1_A</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.001026806905558922</v>
+        <v>0.001047056234053698</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mor11v</t>
+          <t>ATSC8se</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.001024481467136829</v>
+        <v>0.001029975436031257</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ETA_shape_y</t>
+          <t>PEOE_VSA2</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.001023467556020178</v>
+        <v>0.001011463001947614</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AATS0dv</t>
+          <t>Mor15m</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.001021829951002046</v>
+        <v>0.001007425937290123</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PEOE_VSA7</t>
+          <t>AMID_O</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.001006580017643169</v>
+        <v>0.0009979358467184902</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETA_dBeta</t>
+          <t>Mor11</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.001005603955059744</v>
+        <v>0.0009812726995707343</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MATS1Z</t>
+          <t>PEOE_VSA8</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.001005491514892508</v>
+        <v>0.0009746836897307022</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mor29</t>
+          <t>ATSC2Z</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0009676950923330894</v>
+        <v>0.0009460589241350946</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mor26v</t>
+          <t>BCUTd-1l</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0009650142337108153</v>
+        <v>0.0009422228902831076</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SaasC</t>
+          <t>Mor31m</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0009583016700344141</v>
+        <v>0.0009400841824080728</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EState_VSA5</t>
+          <t>Mor13</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0009551520388419681</v>
+        <v>0.0009166803161918804</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ATSC6Z</t>
+          <t>Mor20m</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0009449360073936577</v>
+        <v>0.0009050624065587812</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCUTc-1l</t>
+          <t>Mor12m</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0009444239238370518</v>
+        <v>0.0009048044985584881</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mor20m</t>
+          <t>SIC1</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0009419025567180026</v>
+        <v>0.0008900118529804738</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mor30m</t>
+          <t>Mor10</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0009407831096241843</v>
+        <v>0.0008891168856386939</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MATS2Z</t>
+          <t>Mor04m</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0009362173953270495</v>
+        <v>0.0008864974567762242</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ATSC4c</t>
+          <t>Mor24m</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0009277745049720579</v>
+        <v>0.000884390536162321</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mor32</t>
+          <t>ATSC8dv</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0009191889459023375</v>
+        <v>0.000878432743193051</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mor10</t>
+          <t>Mor16</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0009082274729489166</v>
+        <v>0.0008629123171479198</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mor28</t>
+          <t>ATSC6se</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0009026556920492949</v>
+        <v>0.0008627285130640953</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EState_VSA8</t>
+          <t>EState_VSA5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0008931073646629846</v>
+        <v>0.0008409323702991455</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ATSC1p</t>
+          <t>Mor28</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0008898719059481138</v>
+        <v>0.0008349955060745375</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mor13m</t>
+          <t>Mor26</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0008685773147997508</v>
+        <v>0.00083127463423272</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AMID_O</t>
+          <t>Mor26m</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0008655199011279711</v>
+        <v>0.0008300892174291543</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IC0</t>
+          <t>Mor19m</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0008603390162123163</v>
+        <v>0.0008160653755011425</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ATSC8c</t>
+          <t>ATSC4se</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0008588402076496496</v>
+        <v>0.0008153440887968499</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ATSC4Z</t>
+          <t>Mor11v</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0008542699601046822</v>
+        <v>0.0008098067108949198</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SdssC</t>
+          <t>Mor24</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0008425908963334989</v>
+        <v>0.0008082947804250366</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ATSC7d</t>
+          <t>Mor29m</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0008349535120781437</v>
+        <v>0.0007937842144558959</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mor27m</t>
+          <t>ETA_dBeta</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0008232349559490861</v>
+        <v>0.0007927083592106596</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mor26</t>
+          <t>Mor23m</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0008226806274795898</v>
+        <v>0.0007900164796018862</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mor30</t>
+          <t>GATS1Z</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0008096119729920534</v>
+        <v>0.0007887322544302751</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JGI3</t>
+          <t>GATS2c</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0008061038806653317</v>
+        <v>0.0007870206385910829</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mor09</t>
+          <t>Mor18</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0008017070545625572</v>
+        <v>0.0007759717406856504</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PBF</t>
+          <t>MATS1Z</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0007907026181940142</v>
+        <v>0.0007732299541501305</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GATS2i</t>
+          <t>ATSC5Z</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.00079049463928953</v>
+        <v>0.0007702386636980692</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ATSC5c</t>
+          <t>ATSC2d</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0007832343701200697</v>
+        <v>0.000756538621482694</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mor23m</t>
+          <t>ATSC1i</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0007776834052096936</v>
+        <v>0.0007547130093985955</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ATSC5Z</t>
+          <t>Mor12</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0007636515017902448</v>
+        <v>0.0007479304338493236</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mor10v</t>
+          <t>PBF</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0007587513831601469</v>
+        <v>0.0007399788302680791</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCUTZ-1l</t>
+          <t>SdssC</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0007536693425437208</v>
+        <v>0.0007341518398333816</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BalabanJ</t>
+          <t>PEOE_VSA9</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0007499137805502787</v>
+        <v>0.0007321238476085886</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ATSC3d</t>
+          <t>ATSC4Z</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0007361268969096625</v>
+        <v>0.0007258570007383611</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ATSC8dv</t>
+          <t>ATSC7Z</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0007292535914876483</v>
+        <v>0.0007207819726938421</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mor24m</t>
+          <t>GATS2i</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.000728763932969447</v>
+        <v>0.0007110766325090544</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mor16</t>
+          <t>ATSC2dv</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0007247173892219823</v>
+        <v>0.0007097715920992075</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mor24</t>
+          <t>ATSC5dv</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0007241039122977702</v>
+        <v>0.000707589838938651</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mor12m</t>
+          <t>Mor10m</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0007235439201022815</v>
+        <v>0.0007043616006939223</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GATS2c</t>
+          <t>Mor04</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.000712252677805304</v>
+        <v>0.0006941133276330461</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ATSC5se</t>
+          <t>Mor15</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0006907145146432675</v>
+        <v>0.0006899386212885652</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mor15m</t>
+          <t>ATSC2i</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0006825496160229245</v>
+        <v>0.000689852786424346</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ATSC1i</t>
+          <t>ATSC5se</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0006808538220129878</v>
+        <v>0.000688751981632585</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PEOE_VSA9</t>
+          <t>EState_VSA7</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0006788827809743718</v>
+        <v>0.0006800339718964308</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ATSC8Z</t>
+          <t>Mor27m</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0006778104671699691</v>
+        <v>0.0006779795436095146</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ATSC3se</t>
+          <t>GATS2Z</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0006727204364823576</v>
+        <v>0.000669349983309014</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ATSC2Z</t>
+          <t>VSA_EState5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0006634443683231139</v>
+        <v>0.0006676193230292725</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mor28v</t>
+          <t>Mor09m</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0006576163831143888</v>
+        <v>0.0006671074037513057</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mor11m</t>
+          <t>Mor09</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0006570090738837763</v>
+        <v>0.0006577588969574248</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NaaN</t>
+          <t>Mor18m</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0006483793807185024</v>
+        <v>0.0006573318851469979</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ATSC7se</t>
+          <t>ATSC1p</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0006476336300622021</v>
+        <v>0.0006479231522536944</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mor27</t>
+          <t>ATSC8Z</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.00064046115460303</v>
+        <v>0.000637131671325687</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ATSC6se</t>
+          <t>SpMAD_A</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0006217699955357114</v>
+        <v>0.0006247281991613065</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SlogP_VSA3</t>
+          <t>JGI4</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0006120911649466499</v>
+        <v>0.0006196192321156046</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ATSC5dv</t>
+          <t>ATSC5d</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0006103848306112045</v>
+        <v>0.0006156104039536422</v>
       </c>
     </row>
     <row r="124">
@@ -1667,577 +1667,577 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.0006058731900315317</v>
+        <v>0.0006040929485350198</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ATSC4v</t>
+          <t>Mor22</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0006031889365994187</v>
+        <v>0.0006018192956103758</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SpMAD_A</t>
+          <t>NaaN</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0005967373847022799</v>
+        <v>0.0005994290334649072</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ATSC7Z</t>
+          <t>Mor06</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.000595995691947775</v>
+        <v>0.000596548557318302</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GATS1Z</t>
+          <t>ATSC3d</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0005958720030102082</v>
+        <v>0.000594002046175102</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ATSC3Z</t>
+          <t>ATSC7d</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0005924092883512001</v>
+        <v>0.0005880920779411944</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mor29m</t>
+          <t>Mor28v</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0005880735214949473</v>
+        <v>0.0005856870146843643</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ATSC2d</t>
+          <t>ATSC3Z</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0005850305835941067</v>
+        <v>0.0005805356129270693</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mor10m</t>
+          <t>Mor10v</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0005761896147247984</v>
+        <v>0.0005784055595036571</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ATSC2v</t>
+          <t>PEOE_VSA3</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0005716222841420673</v>
+        <v>0.0005695221420575437</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ATSC5d</t>
+          <t>ATSC8c</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.0005686879724449497</v>
+        <v>0.000566893666620338</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mor25m</t>
+          <t>ATSC4d</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0005641589731165002</v>
+        <v>0.0005660073071366005</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SIC1</t>
+          <t>BCUTZ-1l</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0005616881861880252</v>
+        <v>0.0005646894891706834</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GATS2Z</t>
+          <t>ATSC5v</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.000561117816538301</v>
+        <v>0.0005601675714528823</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mor18</t>
+          <t>Mor13m</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0005566021264205853</v>
+        <v>0.0005549720139823148</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EState_VSA3</t>
+          <t>SlogP_VSA3</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.0005543095795657479</v>
+        <v>0.00054264866173286</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mor15</t>
+          <t>ATSC6i</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.0005494439617844759</v>
+        <v>0.000540118196234537</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ATSC7i</t>
+          <t>ETA_shape_y</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0005368670952821302</v>
+        <v>0.0005377223855498341</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VSA_EState5</t>
+          <t>ATSC5c</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0005359159315438772</v>
+        <v>0.0005308239010194403</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EState_VSA7</t>
+          <t>GATS2v</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0005314517554799286</v>
+        <v>0.0005281132596078244</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Mor18m</t>
+          <t>JGI2</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.000528091979043592</v>
+        <v>0.0005275074405995555</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mor09m</t>
+          <t>Mor08</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0005264246837312517</v>
+        <v>0.0005172490357990821</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AATSC1d</t>
+          <t>ATSC8d</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.0005161333257769702</v>
+        <v>0.0005116036657609095</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ATSC3v</t>
+          <t>VSA_EState4</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0005104783664841404</v>
+        <v>0.0005084032961949715</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ATSC3dv</t>
+          <t>AATSC1d</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0005034004859806822</v>
+        <v>0.0005074657319759059</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ATSC6i</t>
+          <t>ATSC3se</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0005014103807855441</v>
+        <v>0.0005023428575193911</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SlogP_VSA4</t>
+          <t>ATSC5i</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.0004998584873935165</v>
+        <v>0.000500023563792686</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Mor24v</t>
+          <t>ATSC1dv</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0004964128493934678</v>
+        <v>0.0004963392734320645</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ATSC5i</t>
+          <t>Mor11m</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0004868704843334161</v>
+        <v>0.0004908822187407365</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Mor08</t>
+          <t>BalabanJ</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0004866721673474161</v>
+        <v>0.000483868440553555</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ATSC4d</t>
+          <t>ATSC7v</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0004838740526257996</v>
+        <v>0.0004743717305614887</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mor06</t>
+          <t>ATSC8i</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0004828034261564471</v>
+        <v>0.0004713201629032062</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ATSC5v</t>
+          <t>SlogP_VSA7</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.0004615062896337799</v>
+        <v>0.0004603502940137662</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BCUTd-1h</t>
+          <t>ATSC4c</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0004533313427302933</v>
+        <v>0.0004549220125300173</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCUTdv-1l</t>
+          <t>EState_VSA2</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0004529196294920538</v>
+        <v>0.0004548541336080594</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GATS2v</t>
+          <t>Mor30</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0004507611766451422</v>
+        <v>0.0004503166250586486</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EState_VSA2</t>
+          <t>JGI3</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.0004496385591276352</v>
+        <v>0.0004477029629654722</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ATSC6v</t>
+          <t>JGI1</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.0004457201348280892</v>
+        <v>0.0004441020260854658</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ATSC8i</t>
+          <t>BCUTd-1h</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.000444064887407964</v>
+        <v>0.0004427141358693991</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JGI2</t>
+          <t>Mor25m</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0004431496624862394</v>
+        <v>0.0004418158066222479</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mor04</t>
+          <t>Mor24v</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0004423848293182013</v>
+        <v>0.0004385572015533372</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>JGI4</t>
+          <t>ATSC3dv</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.0004377033498135131</v>
+        <v>0.0004369140150677232</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mor22</t>
+          <t>EState_VSA3</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.0004309767664283248</v>
+        <v>0.0004367664517914598</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Mor28m</t>
+          <t>JGI8</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.0004275150322440972</v>
+        <v>0.0004361618128923668</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VSA_EState1</t>
+          <t>ATSC2v</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0004185530241062437</v>
+        <v>0.0004227263003442288</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ATSC7v</t>
+          <t>ATSC1v</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.0004151466514398756</v>
+        <v>0.0004132674183863852</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ATSC6c</t>
+          <t>ATSC4v</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0004124314214893211</v>
+        <v>0.0004113103502157125</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JGI1</t>
+          <t>VSA_EState1</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.0003994957785174376</v>
+        <v>0.0004095344483940119</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>nS</t>
+          <t>ATSC7se</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0003976489349727739</v>
+        <v>0.0004029355580435337</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JGI10</t>
+          <t>ATSC6v</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.000397644688920444</v>
+        <v>0.0004002212770152492</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ATSC1Z</t>
+          <t>SlogP_VSA10</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.0003970076799204025</v>
+        <v>0.0003839580535396563</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nRot</t>
+          <t>JGI9</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.0003932498196776664</v>
+        <v>0.0003837067371522806</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>JGI6</t>
+          <t>BCUTdv-1l</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0003887344801592921</v>
+        <v>0.0003812145186798172</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ATSC2dv</t>
+          <t>Mor28m</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0003885342437972496</v>
+        <v>0.0003752398400425738</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ATSC2i</t>
+          <t>AATS0Z</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.0003799581738848388</v>
+        <v>0.000373171549453559</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ATSC1v</t>
+          <t>SsssCH</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.0003754840438541627</v>
+        <v>0.0003692769420005501</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>GhoseFilter</t>
+          <t>SlogP_VSA4</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.0003680325747419268</v>
+        <v>0.0003626659929584725</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ATSC1dv</t>
+          <t>ATSC7i</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.0003506801683097912</v>
+        <v>0.0003472636730910081</v>
       </c>
     </row>
     <row r="182">
@@ -2247,477 +2247,477 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.0003456116790010406</v>
+        <v>0.0003472350616962815</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>VSA_EState4</t>
+          <t>JGI10</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.0003365180932059764</v>
+        <v>0.0003313505149463599</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JGI8</t>
+          <t>ATSC3v</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0003060549430827697</v>
+        <v>0.0003250737569669181</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SlogP_VSA10</t>
+          <t>PEOE_VSA10</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0003024103399697671</v>
+        <v>0.0003227407488490685</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C1SP2</t>
+          <t>NaasN</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.000280796140683086</v>
+        <v>0.0003154718270727643</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SlogP_VSA1</t>
+          <t>ATSC1Z</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.0002668978022801282</v>
+        <v>0.000314375657193454</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AATS0Z</t>
+          <t>SMR_VSA6</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.0002541676057100416</v>
+        <v>0.0003031315217225923</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NaasC</t>
+          <t>C1SP2</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.0002315878829410822</v>
+        <v>0.0003006318236123663</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>JGI7</t>
+          <t>SlogP_VSA1</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.000229218891913289</v>
+        <v>0.0002845732316266651</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PEOE_VSA10</t>
+          <t>nRot</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.0002205966749803808</v>
+        <v>0.0002800572778309845</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>nN</t>
+          <t>nBondsD</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.0002071301636161499</v>
+        <v>0.0002780274489304031</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C1SP3</t>
+          <t>ATSC6c</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.0002025653719854349</v>
+        <v>0.0002653514075951526</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EState_VSA6</t>
+          <t>ETA_beta_ns_d</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.000201684546506143</v>
+        <v>0.0002525546346596344</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>n10FHRing</t>
+          <t>JGI6</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0001981102285371866</v>
+        <v>0.0002446928713506209</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>JGI9</t>
+          <t>EState_VSA6</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.0001936942832337281</v>
+        <v>0.0002418704840835828</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PEOE_VSA11</t>
+          <t>JGI7</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.0001916391919019317</v>
+        <v>0.000213272615443727</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SsssCH</t>
+          <t>GhoseFilter</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0001879259487191776</v>
+        <v>0.0002031003134636296</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>NaasN</t>
+          <t>nFHRing</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0001825993459890283</v>
+        <v>0.0001966289457508674</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C2SP3</t>
+          <t>nO</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.0001728927276994249</v>
+        <v>0.0001922924205671311</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ETA_beta_ns_d</t>
+          <t>n10FHRing</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.0001606284459061021</v>
+        <v>0.0001914692091008862</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FCSP3</t>
+          <t>Xc-4dv</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.0001572181708530253</v>
+        <v>0.0001908129307173411</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>NssNH</t>
+          <t>C3SP2</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.0001572107572862548</v>
+        <v>0.0001887594803391655</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>nFHRing</t>
+          <t>FCSP3</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.0001512487785098273</v>
+        <v>0.0001874068152991077</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Xc-4d</t>
+          <t>nN</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.0001499437075563997</v>
+        <v>0.0001468554814448158</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NssS</t>
+          <t>nHBDon</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.00013802757340478</v>
+        <v>0.0001455693828368132</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>n5Ring</t>
+          <t>nS</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.0001316408118867662</v>
+        <v>0.0001445311650738771</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PEOE_VSA3</t>
+          <t>n6AHRing</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.0001305841576262732</v>
+        <v>0.000139179037160618</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SMR_VSA6</t>
+          <t>NsssCH</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.0001225934313000122</v>
+        <v>0.0001350435965797642</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>nFRing</t>
+          <t>PEOE_VSA11</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.0001207859457357173</v>
+        <v>0.0001317766606313278</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>nAromAtom</t>
+          <t>PEOE_VSA13</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.0001053648646655636</v>
+        <v>0.000125366359432612</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>nO</t>
+          <t>NaasC</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.0001037022658468435</v>
+        <v>0.0001104078766373176</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SMR_VSA9</t>
+          <t>C2SP3</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>9.434393442922134e-05</v>
+        <v>0.000106818897819108</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xc-4dv</t>
+          <t>NdsCH</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>9.430533804049388e-05</v>
+        <v>9.876203290776958e-05</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>n10FRing</t>
+          <t>NssO</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>9.391727194395687e-05</v>
+        <v>9.754660515816288e-05</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PEOE_VSA13</t>
+          <t>C1SP3</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>8.850294880409318e-05</v>
+        <v>9.325631484935304e-05</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>nAHRing</t>
+          <t>VSA_EState9</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>8.271998323806023e-05</v>
+        <v>8.932693796129207e-05</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NdS</t>
+          <t>Xc-4d</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>6.775319834741427e-05</v>
+        <v>8.100758262843518e-05</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VSA_EState9</t>
+          <t>nP</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>6.338066281550583e-05</v>
+        <v>7.061518409396441e-05</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NsOH</t>
+          <t>nAromAtom</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>6.284914255423481e-05</v>
+        <v>6.829257345441026e-05</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>nFAHRing</t>
+          <t>n5Ring</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>5.99586037769308e-05</v>
+        <v>6.301201262681824e-05</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>n6AHRing</t>
+          <t>NssS</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>5.623605240678376e-05</v>
+        <v>5.843980740329289e-05</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SlogP_VSA7</t>
+          <t>C3SP3</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>5.036494448971363e-05</v>
+        <v>5.483673053126265e-05</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>nBondsD</t>
+          <t>C4SP3</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4.892881196096795e-05</v>
+        <v>4.798503693274353e-05</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NdsCH</t>
+          <t>NsOH</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>4.618760972902601e-05</v>
+        <v>4.638977293190004e-05</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>NsssCH</t>
+          <t>PEOE_VSA5</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>4.161078102027078e-05</v>
+        <v>4.572604229852162e-05</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>NddsN</t>
+          <t>PEOE_VSA4</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>3.800316542378009e-05</v>
+        <v>4.38550498895707e-05</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C4SP3</t>
+          <t>SlogP_VSA11</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>3.669189866286738e-05</v>
+        <v>3.471178338857997e-05</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SlogP_VSA11</t>
+          <t>NssNH</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>3.524097733031543e-05</v>
+        <v>3.289066192138343e-05</v>
       </c>
     </row>
     <row r="230">
@@ -2727,457 +2727,457 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3.396790708495359e-05</v>
+        <v>3.098762962542951e-05</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C3SP2</t>
+          <t>NsssN</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>3.106357713062097e-05</v>
+        <v>2.863285466534876e-05</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PEOE_VSA5</t>
+          <t>n5AHRing</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3.037581518601121e-05</v>
+        <v>2.857000187856382e-05</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>nP</t>
+          <t>SMR_VSA9</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2.769264390625356e-05</v>
+        <v>2.712442387909561e-05</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>nCl</t>
+          <t>n7Ring</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2.513638931939241e-05</v>
+        <v>2.666592979948373e-05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>nHBDon</t>
+          <t>nCl</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2.481265720570904e-05</v>
+        <v>2.542518515408804e-05</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>nF</t>
+          <t>NdS</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2.391919162381689e-05</v>
+        <v>2.358048188557e-05</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>n5AHRing</t>
+          <t>n10FRing</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2.334358674422491e-05</v>
+        <v>2.27242568144131e-05</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>nFaHRing</t>
+          <t>n5HRing</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2.31406525403019e-05</v>
+        <v>2.257768640734962e-05</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C3SP3</t>
+          <t>nFRing</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2.243166808613954e-05</v>
+        <v>2.172653195151492e-05</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>n5HRing</t>
+          <t>n9FRing</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2.029530036309131e-05</v>
+        <v>2.058299161087157e-05</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NsssN</t>
+          <t>nF</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.608567885895374e-05</v>
+        <v>1.199393020469125e-05</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NssO</t>
+          <t>NsNH2</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.543149274207351e-05</v>
+        <v>1.049521373287332e-05</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>NaaaC</t>
+          <t>n5aRing</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1.330169188948977e-05</v>
+        <v>1.038098042164297e-05</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>nSpiro</t>
+          <t>NaaaC</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.151098044449884e-05</v>
+        <v>9.555201244268067e-06</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>n5aRing</t>
+          <t>NdsN</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.143290808894677e-05</v>
+        <v>9.475511023184879e-06</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PEOE_VSA4</t>
+          <t>nFARing</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.074471789441285e-05</v>
+        <v>9.25741026343079e-06</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>n10FARing</t>
+          <t>n10FAHRing</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>8.105118406881577e-06</v>
+        <v>7.672314222221214e-06</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Xch-3d</t>
+          <t>C2SP1</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>5.438680578882899e-06</v>
+        <v>6.813252563076643e-06</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>n9FARing</t>
+          <t>n10FARing</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>4.633555960654199e-06</v>
+        <v>6.676831147972059e-06</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Xch-4d</t>
+          <t>nAHRing</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>4.368742052093199e-06</v>
+        <v>6.606556238547021e-06</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>NaaNH</t>
+          <t>NddsN</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>4.166215378859287e-06</v>
+        <v>5.274920050949282e-06</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>nG12FHRing</t>
+          <t>nFAHRing</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>3.602878713387149e-06</v>
+        <v>4.576936771312645e-06</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>NdsN</t>
+          <t>nBridgehead</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>3.345803172577636e-06</v>
+        <v>4.359644575379731e-06</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>nG12FRing</t>
+          <t>n9FaRing</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>3.312024467483284e-06</v>
+        <v>3.329813763421691e-06</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>NdCH2</t>
+          <t>nG12FRing</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>3.280076192293317e-06</v>
+        <v>2.9446062304528e-06</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>nBondsT</t>
+          <t>n9FARing</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2.883461027205756e-06</v>
+        <v>2.729678821910763e-06</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>nFARing</t>
+          <t>NtN</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2.776222910437036e-06</v>
+        <v>2.577933346525732e-06</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>NsNH2</t>
+          <t>nBondsT</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2.772773890665994e-06</v>
+        <v>2.481448446355182e-06</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>NaaO</t>
+          <t>nFaHRing</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2.662630326737586e-06</v>
+        <v>1.982060148353636e-06</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>NtN</t>
+          <t>NtCH</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>2.372705723703139e-06</v>
+        <v>1.593965169304969e-06</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>C2SP1</t>
+          <t>NaaNH</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2.081746723844519e-06</v>
+        <v>1.416850347660578e-06</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>NtCH</t>
+          <t>nBase</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1.785012662362539e-06</v>
+        <v>1.050220224683075e-06</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>nBr</t>
+          <t>nI</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1.451469246634855e-06</v>
+        <v>9.920098985948442e-07</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>n9FRing</t>
+          <t>Xch-4d</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>9.311810077145369e-07</v>
+        <v>9.341886933876019e-07</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>n11FRing</t>
+          <t>nG12FHRing</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>8.122619228317521e-07</v>
+        <v>6.054443909974307e-07</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>nI</t>
+          <t>NdCH2</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>5.257759014967981e-07</v>
+        <v>5.688482189161073e-07</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>n7Ring</t>
+          <t>NaaO</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>4.819466010962238e-07</v>
+        <v>4.243341932012453e-07</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>n9FaRing</t>
+          <t>n3HRing</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>6.346213282381802e-08</v>
+        <v>3.928858985406424e-07</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>nBridgehead</t>
+          <t>NddssS</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>5.908213295067846e-08</v>
+        <v>3.018143796537367e-07</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>nBase</t>
+          <t>nBr</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>4.198952049675499e-08</v>
+        <v>1.311866460843191e-07</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>n8Ring</t>
+          <t>NsSH</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1.847262295193868e-08</v>
+        <v>1.0986181104913e-07</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>n8FRing</t>
+          <t>n8Ring</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>1.522599155070745e-08</v>
+        <v>8.75226858591356e-08</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>NddssS</t>
+          <t>n12FRing</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>5.67662063574839e-09</v>
+        <v>7.367729961443768e-08</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>nG12FaHRing</t>
+          <t>NaaS</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2.013354254599248e-09</v>
+        <v>5.191101725866123e-08</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>n10FAHRing</t>
+          <t>NdssS</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1.620775078068902e-10</v>
+        <v>4.067235775264886e-08</v>
       </c>
     </row>
     <row r="276">
@@ -3187,43 +3187,43 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>3.508093524528809e-08</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>NaaS</t>
+          <t>n11FRing</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>2.328844875561092e-08</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>NsSH</t>
+          <t>Xch-3d</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>1.877874765563691e-09</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>NdNH</t>
+          <t>nSpiro</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>1.462699309123904e-09</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>NdssS</t>
+          <t>nG12FaHRing</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3233,7 +3233,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>n6FRing</t>
+          <t>NdNH</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -3243,7 +3243,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>n3HRing</t>
+          <t>n6FRing</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -3253,7 +3253,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>n12FRing</t>
+          <t>n8FRing</t>
         </is>
       </c>
       <c r="B283" t="n">

--- a/imp.xlsx
+++ b/imp.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B284"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7198314864812727</v>
+        <v>0.2734944820404053</v>
       </c>
     </row>
     <row r="3">
@@ -457,1147 +457,1147 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04926555841978541</v>
+        <v>0.2013537287712097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RNCG</t>
+          <t>nFRing</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02738199076512673</v>
+        <v>0.03474166616797447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIC0</t>
+          <t>nFHRing</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01678279661849459</v>
+        <v>0.02889524213969707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RPCG</t>
+          <t>nHRing</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01015521877504702</v>
+        <v>0.02616799809038639</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ATS0Z</t>
+          <t>SIC0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003527252964672561</v>
+        <v>0.02180612646043301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JGI5</t>
+          <t>PEOE_VSA6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003427386685605978</v>
+        <v>0.01812831312417984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AETA_eta</t>
+          <t>nFAHRing</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003100126482830602</v>
+        <v>0.01722540333867073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mor02m</t>
+          <t>PEOE_VSA12</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003071434040517759</v>
+        <v>0.01465483009815216</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RNCS</t>
+          <t>RNCG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.00272196428518121</v>
+        <v>0.01342350896447897</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PEOE_VSA6</t>
+          <t>RPCG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002430164482882451</v>
+        <v>0.01258412096649408</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETA_dEpsilon_D</t>
+          <t>JGI5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002334851112888123</v>
+        <v>0.01210650987923145</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FPSA3</t>
+          <t>SlogP_VSA10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002277061151548345</v>
+        <v>0.01107652205973864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AATS0i</t>
+          <t>AATS0se</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002265334089025447</v>
+        <v>0.01000498048961163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AATS0se</t>
+          <t>ETA_dEpsilon_D</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002181598516803452</v>
+        <v>0.00901508703827858</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MATS1c</t>
+          <t>ATSC8v</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002071132448100907</v>
+        <v>0.008720217272639275</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mor22m</t>
+          <t>n7Ring</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002044934513369181</v>
+        <v>0.007223088294267654</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC1</t>
+          <t>Mor16m</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001991386153980218</v>
+        <v>0.006384700071066618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATSC8v</t>
+          <t>n10FRing</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001984453170248523</v>
+        <v>0.006015127990394831</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AATSC0v</t>
+          <t>NdS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001961026246939188</v>
+        <v>0.005911788437515497</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PEOE_VSA12</t>
+          <t>PEOE_VSA7</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001915528251448839</v>
+        <v>0.005885759368538857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC0</t>
+          <t>EState_VSA5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.001842464034987681</v>
+        <v>0.005540926475077868</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nHRing</t>
+          <t>AETA_eta</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.001775022577756296</v>
+        <v>0.00528098177164793</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ATSC7dv</t>
+          <t>Mor31m</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00177083892603931</v>
+        <v>0.00510400952771306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ATSC6dv</t>
+          <t>nP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001770216477181981</v>
+        <v>0.004749100189656019</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SaasC</t>
+          <t>nBondsD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.001750610197467569</v>
+        <v>0.004574412479996681</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GATS1se</t>
+          <t>ATSC1Z</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001703977456023297</v>
+        <v>0.004482659976929426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ATSC1se</t>
+          <t>Mor03m</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001583554948246597</v>
+        <v>0.004285278730094433</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GATS2se</t>
+          <t>IC1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001571924688314876</v>
+        <v>0.004174136091023684</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ATSC3i</t>
+          <t>SdssC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001560790903433062</v>
+        <v>0.004058967810124159</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ATSC4dv</t>
+          <t>ATS0Z</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001522844416422335</v>
+        <v>0.003957842476665974</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PEOE_VSA7</t>
+          <t>ATSC2Z</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001477540542666759</v>
+        <v>0.003742498345673084</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>BCUTZ-1l</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001450057860045733</v>
+        <v>0.003660800401121378</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mor14m</t>
+          <t>Mor04v</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001418156579363753</v>
+        <v>0.003569957334548235</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ATSC7c</t>
+          <t>PEOE_VSA2</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001402673155561526</v>
+        <v>0.003474963596090674</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ATSC6Z</t>
+          <t>ETA_beta_ns_d</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.001318673889878545</v>
+        <v>0.003347277641296387</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AATS0dv</t>
+          <t>ATSC7c</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.001300293708984733</v>
+        <v>0.003053582739084959</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AATSC2Z</t>
+          <t>ATSC6dv</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.00129503408943568</v>
+        <v>0.00303814560174942</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mor32</t>
+          <t>IC0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.00129448211301305</v>
+        <v>0.003021919168531895</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MATS2Z</t>
+          <t>ATSC1v</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.001232134087847298</v>
+        <v>0.002993203699588776</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mor17m</t>
+          <t>PEOE_VSA3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.001211084211327553</v>
+        <v>0.002961362944915891</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ATSC6d</t>
+          <t>SsssCH</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.00120482942898372</v>
+        <v>0.00272805686108768</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mor32m</t>
+          <t>JGI10</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.001199746381469413</v>
+        <v>0.00261529185809195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mor21m</t>
+          <t>PEOE_VSA8</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.001198505835932385</v>
+        <v>0.002552142599597573</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mor30m</t>
+          <t>NaaN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.001169280800721781</v>
+        <v>0.002515220083296299</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RPCS</t>
+          <t>ETA_dBeta</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.001161588014855488</v>
+        <v>0.002406550571322441</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nHetero</t>
+          <t>PBF</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.001148710846320247</v>
+        <v>0.002399311866611242</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mor29</t>
+          <t>AATS0Z</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.001142579539377084</v>
+        <v>0.002332792617380619</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mor26v</t>
+          <t>Mor04m</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.00114133536179568</v>
+        <v>0.002323232591152191</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EState_VSA4</t>
+          <t>Mor02m</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.001141181832125424</v>
+        <v>0.002268994459882379</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mor27</t>
+          <t>AMID_O</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.00114081585881781</v>
+        <v>0.002227057237178087</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mor04v</t>
+          <t>MATS1c</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.001125046026919892</v>
+        <v>0.002199099631980062</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AATSC0i</t>
+          <t>C3SP3</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.001121387981094643</v>
+        <v>0.002189571736380458</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCUTc-1l</t>
+          <t>Mor07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.001117316113650834</v>
+        <v>0.002164581790566444</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mor06m</t>
+          <t>GATS2se</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.001107090818040895</v>
+        <v>0.002161043463274837</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GeomShapeIndex</t>
+          <t>Mor21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.001089582234277316</v>
+        <v>0.002057609148323536</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EState_VSA8</t>
+          <t>GATS2Z</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.00105963805637794</v>
+        <v>0.002056793076917529</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ATSC2c</t>
+          <t>nHetero</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.001056216187527707</v>
+        <v>0.001908727805130184</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VR1_A</t>
+          <t>GATS1Z</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.001047056234053698</v>
+        <v>0.001890283660031855</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ATSC8se</t>
+          <t>Mor11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.001029975436031257</v>
+        <v>0.00187588413245976</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PEOE_VSA2</t>
+          <t>AATS0i</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.001011463001947614</v>
+        <v>0.001870680600404739</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mor15m</t>
+          <t>C1SP3</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.001007425937290123</v>
+        <v>0.001843114150688052</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMID_O</t>
+          <t>Mor09</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0009979358467184902</v>
+        <v>0.001840537064708769</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mor11</t>
+          <t>AATSC0v</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0009812726995707343</v>
+        <v>0.001809643465094268</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEOE_VSA8</t>
+          <t>AATSC0i</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0009746836897307022</v>
+        <v>0.001776656252332032</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ATSC2Z</t>
+          <t>FPSA3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0009460589241350946</v>
+        <v>0.001706061419099569</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCUTd-1l</t>
+          <t>JGI1</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0009422228902831076</v>
+        <v>0.001662479829974473</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mor31m</t>
+          <t>Mor11m</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0009400841824080728</v>
+        <v>0.001628310070373118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mor13</t>
+          <t>ATSC5d</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0009166803161918804</v>
+        <v>0.001599386218003929</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mor20m</t>
+          <t>NaasN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0009050624065587812</v>
+        <v>0.001595856505446136</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mor12m</t>
+          <t>RNCS</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0009048044985584881</v>
+        <v>0.001595662906765938</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SIC1</t>
+          <t>EState_VSA7</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0008900118529804738</v>
+        <v>0.001573828514665365</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mor10</t>
+          <t>nRot</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0008891168856386939</v>
+        <v>0.001546374289318919</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mor04m</t>
+          <t>NaasC</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0008864974567762242</v>
+        <v>0.001528535387478769</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mor24m</t>
+          <t>ATSC6d</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.000884390536162321</v>
+        <v>0.001526582869701087</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ATSC8dv</t>
+          <t>ATSC7se</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.000878432743193051</v>
+        <v>0.001525838277302682</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mor16</t>
+          <t>SMR_VSA6</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0008629123171479198</v>
+        <v>0.001517841825261712</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ATSC6se</t>
+          <t>Mor15</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0008627285130640953</v>
+        <v>0.00150616595055908</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EState_VSA5</t>
+          <t>EState_VSA2</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0008409323702991455</v>
+        <v>0.001492118346504867</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mor28</t>
+          <t>NsOH</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0008349955060745375</v>
+        <v>0.001488634035922587</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mor26</t>
+          <t>ATSC8se</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.00083127463423272</v>
+        <v>0.001454715034924448</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mor26m</t>
+          <t>SlogP_VSA3</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0008300892174291543</v>
+        <v>0.001413122285157442</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mor19m</t>
+          <t>ATSC2c</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0008160653755011425</v>
+        <v>0.001396008534356952</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ATSC4se</t>
+          <t>JGI2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0008153440887968499</v>
+        <v>0.001379507477395236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mor11v</t>
+          <t>MATS2Z</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0008098067108949198</v>
+        <v>0.0013794070109725</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mor24</t>
+          <t>Mor26m</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0008082947804250366</v>
+        <v>0.00135834573302418</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mor29m</t>
+          <t>BCUTd-1l</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0007937842144558959</v>
+        <v>0.001349427970126271</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ETA_dBeta</t>
+          <t>ATSC7Z</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0007927083592106596</v>
+        <v>0.001345053082332015</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mor23m</t>
+          <t>ATSC3i</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0007900164796018862</v>
+        <v>0.001341609284281731</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GATS1Z</t>
+          <t>BCUTdv-1l</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0007887322544302751</v>
+        <v>0.001334854052402079</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GATS2c</t>
+          <t>Mor14m</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0007870206385910829</v>
+        <v>0.001270409789867699</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mor18</t>
+          <t>ATSC8Z</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0007759717406856504</v>
+        <v>0.001249857246875763</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MATS1Z</t>
+          <t>GATS1se</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0007732299541501305</v>
+        <v>0.00124347407836467</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ATSC5Z</t>
+          <t>Mor29m</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.0007702386636980692</v>
+        <v>0.00123660743702203</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ATSC2d</t>
+          <t>VSA_EState9</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.000756538621482694</v>
+        <v>0.001219505094923079</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ATSC1i</t>
+          <t>BCUTc-1l</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0007547130093985955</v>
+        <v>0.001206211978569627</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mor12</t>
+          <t>Mor10v</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0007479304338493236</v>
+        <v>0.001191113493405282</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PBF</t>
+          <t>JGI6</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0007399788302680791</v>
+        <v>0.001181140076369047</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SdssC</t>
+          <t>ATSC3se</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0007341518398333816</v>
+        <v>0.001156701473519206</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PEOE_VSA9</t>
+          <t>ATSC7d</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0007321238476085886</v>
+        <v>0.00115192832890898</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ATSC4Z</t>
+          <t>VR1_A</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0007258570007383611</v>
+        <v>0.00114755891263485</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ATSC7Z</t>
+          <t>NsssN</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0007207819726938421</v>
+        <v>0.001147521892562509</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GATS2i</t>
+          <t>ATSC5c</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0007110766325090544</v>
+        <v>0.001115719438530505</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ATSC2dv</t>
+          <t>Mor17m</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0007097715920992075</v>
+        <v>0.001097950735129416</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ATSC5dv</t>
+          <t>SIC1</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.000707589838938651</v>
+        <v>0.001090290024876595</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mor10m</t>
+          <t>Mor05m</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0007043616006939223</v>
+        <v>0.001044070930220187</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mor04</t>
+          <t>ATSC1se</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0006941133276330461</v>
+        <v>0.001036851550452411</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mor15</t>
+          <t>GATS2c</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0006899386212885652</v>
+        <v>0.001028345781378448</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ATSC2i</t>
+          <t>Mor25</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.000689852786424346</v>
+        <v>0.001015019952319562</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ATSC5se</t>
+          <t>PEOE_VSA9</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.000688751981632585</v>
+        <v>0.001013258239254355</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EState_VSA7</t>
+          <t>Mor15m</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0006800339718964308</v>
+        <v>0.0010046421084553</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mor27m</t>
+          <t>ATSC6se</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0006779795436095146</v>
+        <v>0.0009792189812287688</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GATS2Z</t>
+          <t>n9FRing</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.000669349983309014</v>
+        <v>0.0009762255358509719</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VSA_EState5</t>
+          <t>Mor28m</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0006676193230292725</v>
+        <v>0.000971487199421972</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mor09m</t>
+          <t>Mor22m</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0006671074037513057</v>
+        <v>0.0009648367995396256</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mor09</t>
+          <t>Mor20</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0006577588969574248</v>
+        <v>0.0009645563550293446</v>
       </c>
     </row>
     <row r="118">
@@ -1607,1623 +1607,1623 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0006573318851469979</v>
+        <v>0.0009604833321645856</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ATSC1p</t>
+          <t>ATSC1i</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0006479231522536944</v>
+        <v>0.0009384782169945538</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ATSC8Z</t>
+          <t>JGI4</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.000637131671325687</v>
+        <v>0.0009193450096063316</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SpMAD_A</t>
+          <t>SlogP_VSA11</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0006247281991613065</v>
+        <v>0.0009034849354065955</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JGI4</t>
+          <t>ATSC8d</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0006196192321156046</v>
+        <v>0.0008932086639106274</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ATSC5d</t>
+          <t>SaasC</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0006156104039536422</v>
+        <v>0.0008928122697398067</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mor16m</t>
+          <t>ATSC6i</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.0006040929485350198</v>
+        <v>0.0008806943078525364</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Mor22</t>
+          <t>SMR_VSA9</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0006018192956103758</v>
+        <v>0.0008803530363366008</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NaaN</t>
+          <t>Mor26</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0005994290334649072</v>
+        <v>0.0008784847450442612</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mor06</t>
+          <t>ATSC7i</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.000596548557318302</v>
+        <v>0.0008739129989407957</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ATSC3d</t>
+          <t>ATSC5dv</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.000594002046175102</v>
+        <v>0.000867981871124357</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ATSC7d</t>
+          <t>ATSC8c</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0005880920779411944</v>
+        <v>0.0008625297923572361</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mor28v</t>
+          <t>ATSC4dv</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0005856870146843643</v>
+        <v>0.0008576630498282611</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ATSC3Z</t>
+          <t>FCSP3</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0005805356129270693</v>
+        <v>0.0008555753156542778</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mor10v</t>
+          <t>ATSC2v</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0005784055595036571</v>
+        <v>0.000848717347253114</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PEOE_VSA3</t>
+          <t>EState_VSA6</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0005695221420575437</v>
+        <v>0.0008458918891847134</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ATSC8c</t>
+          <t>MATS1Z</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.000566893666620338</v>
+        <v>0.0008429782465100288</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ATSC4d</t>
+          <t>NsssCH</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0005660073071366005</v>
+        <v>0.0007914163870736957</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCUTZ-1l</t>
+          <t>BalabanJ</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0005646894891706834</v>
+        <v>0.0007913743029348552</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ATSC5v</t>
+          <t>Mor23m</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.0005601675714528823</v>
+        <v>0.0007885756785981357</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mor13m</t>
+          <t>GATS2i</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0005549720139823148</v>
+        <v>0.0007855495205149055</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SlogP_VSA3</t>
+          <t>EState_VSA3</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.00054264866173286</v>
+        <v>0.0007806764915585518</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ATSC6i</t>
+          <t>Mor10</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.000540118196234537</v>
+        <v>0.0007714213570579886</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ETA_shape_y</t>
+          <t>ATSC4d</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0005377223855498341</v>
+        <v>0.0007632873021066189</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ATSC5c</t>
+          <t>JGI3</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0005308239010194403</v>
+        <v>0.0007600425742566586</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GATS2v</t>
+          <t>ATSC1p</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0005281132596078244</v>
+        <v>0.000754214299377054</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JGI2</t>
+          <t>ATSC3Z</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.0005275074405995555</v>
+        <v>0.0007534270989708602</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mor08</t>
+          <t>Mor02</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0005172490357990821</v>
+        <v>0.0007372823311015964</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ATSC8d</t>
+          <t>NdsCH</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.0005116036657609095</v>
+        <v>0.0007268277695402503</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>VSA_EState4</t>
+          <t>AATSC1d</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0005084032961949715</v>
+        <v>0.0007198181701824069</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AATSC1d</t>
+          <t>Mor06</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0005074657319759059</v>
+        <v>0.0007155344355851412</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ATSC3se</t>
+          <t>C2SP3</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0005023428575193911</v>
+        <v>0.0006953314878046513</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ATSC5i</t>
+          <t>Mor24</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.000500023563792686</v>
+        <v>0.0006874419050291181</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ATSC1dv</t>
+          <t>ATSC6v</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0004963392734320645</v>
+        <v>0.0006662209052592516</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Mor11m</t>
+          <t>ATSC7dv</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0004908822187407365</v>
+        <v>0.0006593339494429529</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BalabanJ</t>
+          <t>Mor28</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.000483868440553555</v>
+        <v>0.0006476715207099915</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ATSC7v</t>
+          <t>Mor30m</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0004743717305614887</v>
+        <v>0.0006271177553571761</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ATSC8i</t>
+          <t>JGI7</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0004713201629032062</v>
+        <v>0.0006151341367512941</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SlogP_VSA7</t>
+          <t>AETA_eta_RL</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.0004603502940137662</v>
+        <v>0.0006091110990382731</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ATSC4c</t>
+          <t>GeomShapeIndex</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0004549220125300173</v>
+        <v>0.0006086709327064455</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EState_VSA2</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0004548541336080594</v>
+        <v>0.0006040468579158187</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mor30</t>
+          <t>Mor23</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0004503166250586486</v>
+        <v>0.0005977881955914199</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JGI3</t>
+          <t>ATSC3dv</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.0004477029629654722</v>
+        <v>0.0005831286543980241</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JGI1</t>
+          <t>ATSC2dv</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.0004441020260854658</v>
+        <v>0.0005812564049847424</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCUTd-1h</t>
+          <t>ATSC3d</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.0004427141358693991</v>
+        <v>0.0005812251474708319</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mor25m</t>
+          <t>Mor12m</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0004418158066222479</v>
+        <v>0.00055395916569978</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mor24v</t>
+          <t>RPCS</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0004385572015533372</v>
+        <v>0.0005515223019756377</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ATSC3dv</t>
+          <t>ATSC8dv</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.0004369140150677232</v>
+        <v>0.0005499030230566859</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>EState_VSA3</t>
+          <t>Mor21m</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.0004367664517914598</v>
+        <v>0.0005475743091665208</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JGI8</t>
+          <t>Mor08</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.0004361618128923668</v>
+        <v>0.0005183696048334241</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ATSC2v</t>
+          <t>AATSC2Z</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0004227263003442288</v>
+        <v>0.0005019311793148518</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ATSC1v</t>
+          <t>AATS0dv</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.0004132674183863852</v>
+        <v>0.0004993683542124927</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ATSC4v</t>
+          <t>ATSC4c</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0004113103502157125</v>
+        <v>0.0004885341040790081</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VSA_EState1</t>
+          <t>Mor32</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.0004095344483940119</v>
+        <v>0.0004718353447970003</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ATSC7se</t>
+          <t>Mor16v</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0004029355580435337</v>
+        <v>0.0004678275436162949</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ATSC6v</t>
+          <t>ATSC2i</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.0004002212770152492</v>
+        <v>0.0004640264669433236</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SlogP_VSA10</t>
+          <t>ETA_shape_y</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.0003839580535396563</v>
+        <v>0.0004608118906617165</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JGI9</t>
+          <t>ATSC4Z</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.0003837067371522806</v>
+        <v>0.0004573966725729406</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BCUTdv-1l</t>
+          <t>ATSC5se</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.0003812145186798172</v>
+        <v>0.0004573850601445884</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mor28m</t>
+          <t>C1SP2</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0003752398400425738</v>
+        <v>0.000453141750767827</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AATS0Z</t>
+          <t>ATSC4se</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.000373171549453559</v>
+        <v>0.0004429064865689725</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SsssCH</t>
+          <t>Xc-4d</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.0003692769420005501</v>
+        <v>0.0004419751348905265</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SlogP_VSA4</t>
+          <t>VSA_EState1</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.0003626659929584725</v>
+        <v>0.0004343752225395292</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ATSC7i</t>
+          <t>Mor30</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.0003472636730910081</v>
+        <v>0.0004313134122639894</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AETA_eta_RL</t>
+          <t>Mor25m</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.0003472350616962815</v>
+        <v>0.0004143003025092185</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>JGI10</t>
+          <t>Mor24v</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.0003313505149463599</v>
+        <v>0.0004100188962183893</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ATSC3v</t>
+          <t>ATSC6Z</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.0003250737569669181</v>
+        <v>0.0004091680457349867</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PEOE_VSA10</t>
+          <t>Mor09m</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.0003227407488490685</v>
+        <v>0.000408410414820537</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NaasN</t>
+          <t>Mor20m</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.0003154718270727643</v>
+        <v>0.0004037786857225001</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ATSC1Z</t>
+          <t>Mor13</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.000314375657193454</v>
+        <v>0.0003881868033204228</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SMR_VSA6</t>
+          <t>ATSC5Z</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.0003031315217225923</v>
+        <v>0.0003876054252032191</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C1SP2</t>
+          <t>ATSC6c</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.0003006318236123663</v>
+        <v>0.0003859948192257434</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SlogP_VSA1</t>
+          <t>PEOE_VSA11</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.0002845732316266651</v>
+        <v>0.0003801230923272669</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>nRot</t>
+          <t>GATS2v</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.0002800572778309845</v>
+        <v>0.0003763305430766195</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>nBondsD</t>
+          <t>Mor16</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.0002780274489304031</v>
+        <v>0.0003735526115633547</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ATSC6c</t>
+          <t>ATSC4v</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.0002653514075951526</v>
+        <v>0.000367370288586244</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ETA_beta_ns_d</t>
+          <t>VSA_EState4</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.0002525546346596344</v>
+        <v>0.0003665796539280564</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>JGI6</t>
+          <t>Mor19m</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0002446928713506209</v>
+        <v>0.0003581870987545699</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EState_VSA6</t>
+          <t>EState_VSA4</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.0002418704840835828</v>
+        <v>0.0003507294459268451</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>JGI7</t>
+          <t>Mor24m</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.000213272615443727</v>
+        <v>0.0003503803454805166</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>GhoseFilter</t>
+          <t>Mor22v</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0002031003134636296</v>
+        <v>0.00034305130247958</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>nFHRing</t>
+          <t>Mor06m</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0001966289457508674</v>
+        <v>0.0003423883172217757</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>nO</t>
+          <t>ATSC3v</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.0001922924205671311</v>
+        <v>0.0003397011023480445</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>n10FHRing</t>
+          <t>Mor13m</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.0001914692091008862</v>
+        <v>0.0003353847714606673</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Xc-4dv</t>
+          <t>SlogP_VSA4</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.0001908129307173411</v>
+        <v>0.0003341096744406968</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C3SP2</t>
+          <t>Mor32m</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.0001887594803391655</v>
+        <v>0.0003303635457996279</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FCSP3</t>
+          <t>ATSC7v</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.0001874068152991077</v>
+        <v>0.0003197772894054651</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>nN</t>
+          <t>BCUTd-1h</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.0001468554814448158</v>
+        <v>0.0003132783458568156</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>nHBDon</t>
+          <t>Mor27m</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.0001455693828368132</v>
+        <v>0.0003066974750254303</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>nS</t>
+          <t>ATSC1dv</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.0001445311650738771</v>
+        <v>0.0002956320822704583</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>n6AHRing</t>
+          <t>Mor10m</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.000139179037160618</v>
+        <v>0.0002885897702071816</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NsssCH</t>
+          <t>ATSC5v</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.0001350435965797642</v>
+        <v>0.0002848344447556883</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PEOE_VSA11</t>
+          <t>JGI9</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.0001317766606313278</v>
+        <v>0.0002832741301972419</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PEOE_VSA13</t>
+          <t>n10FHRing</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.000125366359432612</v>
+        <v>0.0002803718962240964</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NaasC</t>
+          <t>GhoseFilter</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.0001104078766373176</v>
+        <v>0.0002686271909624338</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C2SP3</t>
+          <t>Mor22</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.000106818897819108</v>
+        <v>0.0002600029401946813</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>NdsCH</t>
+          <t>Mor11v</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>9.876203290776958e-05</v>
+        <v>0.0002554865495767444</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>NssO</t>
+          <t>NsCH3</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>9.754660515816288e-05</v>
+        <v>0.0002473926870152354</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C1SP3</t>
+          <t>ATSC5i</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>9.325631484935304e-05</v>
+        <v>0.0002251294208690524</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VSA_EState9</t>
+          <t>EState_VSA8</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>8.932693796129207e-05</v>
+        <v>0.0002068917528958991</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Xc-4d</t>
+          <t>nFARing</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>8.100758262843518e-05</v>
+        <v>0.0001875970046967268</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>nP</t>
+          <t>Mor27</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>7.061518409396441e-05</v>
+        <v>0.000186691278940998</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>nAromAtom</t>
+          <t>Mor30v</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>6.829257345441026e-05</v>
+        <v>0.0001779931772034615</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>n5Ring</t>
+          <t>nO</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>6.301201262681824e-05</v>
+        <v>0.0001739254948915914</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NssS</t>
+          <t>NsSH</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>5.843980740329289e-05</v>
+        <v>0.000167654114193283</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C3SP3</t>
+          <t>PEOE_VSA10</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>5.483673053126265e-05</v>
+        <v>0.0001608674501767382</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C4SP3</t>
+          <t>nN</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4.798503693274353e-05</v>
+        <v>0.0001565183774800971</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NsOH</t>
+          <t>SpMAD_A</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>4.638977293190004e-05</v>
+        <v>0.0001518475764896721</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PEOE_VSA5</t>
+          <t>Xc-4dv</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>4.572604229852162e-05</v>
+        <v>0.0001472604926675558</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PEOE_VSA4</t>
+          <t>SlogP_VSA1</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>4.38550498895707e-05</v>
+        <v>0.0001459933264413849</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SlogP_VSA11</t>
+          <t>ATSC2d</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>3.471178338857997e-05</v>
+        <v>0.0001182706910185516</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NssNH</t>
+          <t>NaaO</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>3.289066192138343e-05</v>
+        <v>0.000111259680124931</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NsCH3</t>
+          <t>VSA_EState5</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3.098762962542951e-05</v>
+        <v>0.0001064499883796088</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NsssN</t>
+          <t>ATSC8i</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2.863285466534876e-05</v>
+        <v>0.0001021503267111257</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>n5AHRing</t>
+          <t>nS</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2.857000187856382e-05</v>
+        <v>8.88191134436056e-05</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SMR_VSA9</t>
+          <t>nHBDon</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2.712442387909561e-05</v>
+        <v>6.275057239690796e-05</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>n7Ring</t>
+          <t>PEOE_VSA5</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2.666592979948373e-05</v>
+        <v>5.663761112373322e-05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>nCl</t>
+          <t>nFaHRing</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2.542518515408804e-05</v>
+        <v>4.820264439331368e-05</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NdS</t>
+          <t>PEOE_VSA13</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2.358048188557e-05</v>
+        <v>4.104569234186783e-05</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>n10FRing</t>
+          <t>nBridgehead</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2.27242568144131e-05</v>
+        <v>2.712582863750868e-05</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>n5HRing</t>
+          <t>NaaNH</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2.257768640734962e-05</v>
+        <v>2.694041540962644e-05</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>nFRing</t>
+          <t>nBase</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2.172653195151492e-05</v>
+        <v>2.103601764247287e-05</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>n9FRing</t>
+          <t>NdsN</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2.058299161087157e-05</v>
+        <v>1.935394175234251e-05</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>nF</t>
+          <t>JGI8</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.199393020469125e-05</v>
+        <v>1.782465369615238e-05</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NsNH2</t>
+          <t>nCl</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.049521373287332e-05</v>
+        <v>1.621357478143182e-05</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>n5aRing</t>
+          <t>nBr</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1.038098042164297e-05</v>
+        <v>1.529622568341438e-05</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>NaaaC</t>
+          <t>nAromAtom</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>9.555201244268067e-06</v>
+        <v>9.379014954902232e-06</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>NdsN</t>
+          <t>NssO</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9.475511023184879e-06</v>
+        <v>9.205875358020421e-06</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>nFARing</t>
+          <t>nF</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>9.25741026343079e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>n10FAHRing</t>
+          <t>nI</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>7.672314222221214e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C2SP1</t>
+          <t>nSpiro</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>6.813252563076643e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>n10FARing</t>
+          <t>NdNH</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>6.676831147972059e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>nAHRing</t>
+          <t>C4SP3</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>6.606556238547021e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>NddsN</t>
+          <t>C3SP2</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>5.274920050949282e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>nFAHRing</t>
+          <t>Xch-4d</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>4.576936771312645e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>nBridgehead</t>
+          <t>nBondsT</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>4.359644575379731e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>n9FaRing</t>
+          <t>Xch-3d</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>3.329813763421691e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>nG12FRing</t>
+          <t>n8FRing</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>2.9446062304528e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>n9FARing</t>
+          <t>n7FRing</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2.729678821910763e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>NtN</t>
+          <t>C2SP1</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2.577933346525732e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>nBondsT</t>
+          <t>NddsN</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2.481448446355182e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>nFaHRing</t>
+          <t>NtN</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>1.982060148353636e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>NtCH</t>
+          <t>NssNH</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1.593965169304969e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>NaaNH</t>
+          <t>NdCH2</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1.416850347660578e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>nBase</t>
+          <t>NtCH</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>1.050220224683075e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>nI</t>
+          <t>NaaaC</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>9.920098985948442e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Xch-4d</t>
+          <t>NsNH2</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>9.341886933876019e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>nG12FHRing</t>
+          <t>NssS</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>6.054443909974307e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>NdCH2</t>
+          <t>NdssS</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>5.688482189161073e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>NaaO</t>
+          <t>NddssS</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>4.243341932012453e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>n3HRing</t>
+          <t>NaaS</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3.928858985406424e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NddssS</t>
+          <t>PEOE_VSA4</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>3.018143796537367e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>nBr</t>
+          <t>n10FAHRing</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1.311866460843191e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>NsSH</t>
+          <t>n10FARing</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>1.0986181104913e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>n8Ring</t>
+          <t>SlogP_VSA7</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>8.75226858591356e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>n12FRing</t>
+          <t>n5Ring</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>7.367729961443768e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>NaaS</t>
+          <t>n5aRing</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>5.191101725866123e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NdssS</t>
+          <t>n5HRing</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>4.067235775264886e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>n12FHRing</t>
+          <t>n3HRing</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3.508093524528809e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>n11FRing</t>
+          <t>n8Ring</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>2.328844875561092e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Xch-3d</t>
+          <t>n6FRing</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1.877874765563691e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>nSpiro</t>
+          <t>nAHRing</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1.462699309123904e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>nG12FaHRing</t>
+          <t>n6AHRing</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -3233,7 +3233,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>NdNH</t>
+          <t>n5AHRing</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -3243,7 +3243,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>n6FRing</t>
+          <t>nG12FRing</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -3253,7 +3253,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>n8FRing</t>
+          <t>n12FRing</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -3263,10 +3263,60 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>n7FRing</t>
+          <t>n11FRing</t>
         </is>
       </c>
       <c r="B284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>n12FHRing</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>n9FaRing</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>nG12FHRing</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>nG12FaHRing</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>n9FARing</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
         <v>0</v>
       </c>
     </row>
